--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,357 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122396074</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90799</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skomakarens kärr, Skomakarens kärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>632676</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6556323</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122419281</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56584</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djupsjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>632640</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6556322</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Rolf Wahlström, Johan Björkstén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122419173</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56584</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djupsjön, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>632662</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6556370</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En vingpenna.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Rolf Wahlström, Johan Björkstén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90799</v>
+        <v>90809</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90799</v>
+        <v>90809</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122419281</v>
+        <v>122419173</v>
       </c>
       <c r="B4" t="n">
         <v>56584</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632640</v>
+        <v>632662</v>
       </c>
       <c r="R4" t="n">
-        <v>6556322</v>
+        <v>6556370</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färsk spillning.</t>
+          <t>En vingpenna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122419173</v>
+        <v>122419281</v>
       </c>
       <c r="B5" t="n">
         <v>56584</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632662</v>
+        <v>632640</v>
       </c>
       <c r="R5" t="n">
-        <v>6556370</v>
+        <v>6556322</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En vingpenna.</t>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>122419173</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>122419281</v>
       </c>
       <c r="B5" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90828</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>5442</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -783,7 +778,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90828</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,11 +792,6 @@
       </c>
       <c r="E3" t="n">
         <v>5442</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -901,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122419173</v>
+        <v>122419281</v>
       </c>
       <c r="B4" t="n">
         <v>56589</v>
@@ -918,11 +908,6 @@
       </c>
       <c r="E4" t="n">
         <v>100138</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -949,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632662</v>
+        <v>632640</v>
       </c>
       <c r="R4" t="n">
-        <v>6556370</v>
+        <v>6556322</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En vingpenna.</t>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122419281</v>
+        <v>122419173</v>
       </c>
       <c r="B5" t="n">
         <v>56589</v>
@@ -1033,11 +1018,6 @@
       </c>
       <c r="E5" t="n">
         <v>100138</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1064,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632640</v>
+        <v>632662</v>
       </c>
       <c r="R5" t="n">
-        <v>6556322</v>
+        <v>6556370</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk spillning.</t>
+          <t>En vingpenna.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>90846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>5442</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -778,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -792,6 +797,11 @@
       </c>
       <c r="E3" t="n">
         <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -891,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122419281</v>
+        <v>122419173</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,6 +918,11 @@
       </c>
       <c r="E4" t="n">
         <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -934,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632640</v>
+        <v>632662</v>
       </c>
       <c r="R4" t="n">
-        <v>6556322</v>
+        <v>6556370</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färsk spillning.</t>
+          <t>En vingpenna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122419173</v>
+        <v>122419281</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,6 +1033,11 @@
       </c>
       <c r="E5" t="n">
         <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1044,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632662</v>
+        <v>632640</v>
       </c>
       <c r="R5" t="n">
-        <v>6556370</v>
+        <v>6556322</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En vingpenna.</t>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122419173</v>
+        <v>122419281</v>
       </c>
       <c r="B4" t="n">
         <v>56593</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632662</v>
+        <v>632640</v>
       </c>
       <c r="R4" t="n">
-        <v>6556370</v>
+        <v>6556322</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En vingpenna.</t>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122419281</v>
+        <v>122419173</v>
       </c>
       <c r="B5" t="n">
         <v>56593</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632640</v>
+        <v>632662</v>
       </c>
       <c r="R5" t="n">
-        <v>6556322</v>
+        <v>6556370</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk spillning.</t>
+          <t>En vingpenna.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122419281</v>
+        <v>122419173</v>
       </c>
       <c r="B4" t="n">
         <v>56593</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632640</v>
+        <v>632662</v>
       </c>
       <c r="R4" t="n">
-        <v>6556322</v>
+        <v>6556370</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färsk spillning.</t>
+          <t>En vingpenna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122419173</v>
+        <v>122419281</v>
       </c>
       <c r="B5" t="n">
         <v>56593</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632662</v>
+        <v>632640</v>
       </c>
       <c r="R5" t="n">
-        <v>6556370</v>
+        <v>6556322</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En vingpenna.</t>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122263446</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122419281</v>
+        <v>122419173</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632640</v>
+        <v>632662</v>
       </c>
       <c r="R4" t="n">
-        <v>6556322</v>
+        <v>6556370</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färsk spillning.</t>
+          <t>En vingpenna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122419173</v>
+        <v>122419281</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632662</v>
+        <v>632640</v>
       </c>
       <c r="R5" t="n">
-        <v>6556370</v>
+        <v>6556322</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En vingpenna.</t>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>122396074</v>
       </c>
       <c r="B3" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122419173</v>
+        <v>122419281</v>
       </c>
       <c r="B4" t="n">
         <v>56594</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632662</v>
+        <v>632640</v>
       </c>
       <c r="R4" t="n">
-        <v>6556370</v>
+        <v>6556322</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En vingpenna.</t>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122419281</v>
+        <v>122419173</v>
       </c>
       <c r="B5" t="n">
         <v>56594</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632640</v>
+        <v>632662</v>
       </c>
       <c r="R5" t="n">
-        <v>6556322</v>
+        <v>6556370</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk spillning.</t>
+          <t>En vingpenna.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1702-2025 artfynd.xlsx
+++ b/artfynd/A 1702-2025 artfynd.xlsx
@@ -904,12 +904,7 @@
         <v>122419173</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,12 +1014,7 @@
         <v>122419281</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
